--- a/naver-place-crawler/results_nail/서면_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/서면_네일샵.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>손더네일 속눈썹 서면본점</t>
+          <t>르엘유네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sonthenail@naver.com</t>
+          <t>yen3355_@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1331-5688</t>
+          <t>0507-1388-2770</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로 22 1층 손더네일 속눈썹 서면본점</t>
+          <t>부산광역시 부산진구 서전로38번길 9-10 A동 1층 107호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sonthenail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1613</v>
+        <v>118</v>
       </c>
       <c r="Q2" t="n">
-        <v>2896</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>4509</v>
+        <v>125</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>34897918</t>
+          <t>1249178449</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34897918</t>
+          <t>https://m.place.naver.com/place/1249178449</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일쏭 서면본점</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wun_0730@naver.com</t>
+          <t>ysbfly@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1373-1142</t>
+          <t>0507-1328-0573</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 69-1 3층 nail쏭</t>
+          <t>부산광역시 동구 중앙대로 225-1 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_song0707</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1617</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>3337</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4954</v>
+        <v>8</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1110913709</t>
+          <t>1113758874</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1110913709</t>
+          <t>https://m.place.naver.com/place/1113758874</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>손끝에서 NAIL&amp;BEAUTY</t>
+          <t>언제나 네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>freeseok80@naver.com</t>
+          <t>cssyou@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1332-7220</t>
+          <t>0507-1420-2902</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 전포대로209번길 43 아세아빌딩 3층 손끝에서</t>
+          <t>부산광역시 동구 범일로 98-2 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/from.my_hand</t>
+          <t>https://www.instagram.com/always_nail_24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3817</v>
+        <v>480</v>
       </c>
       <c r="Q4" t="n">
-        <v>2223</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>6040</v>
+        <v>483</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1893558568</t>
+          <t>1198514565</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1893558568</t>
+          <t>https://m.place.naver.com/place/1198514565</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엠씨네일 서면점</t>
+          <t>네일 루피투애비 서면전포본점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>soulkangs@naver.com</t>
+          <t>lufi_tuae_b@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1427-7812</t>
+          <t>0507-1400-4042</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 87 3층 301호</t>
+          <t>부산광역시 부산진구 서전로68번길 64 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mc_nail2017/</t>
+          <t>https://blog.naver.com/lufi_tuae_b</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1595</v>
+        <v>175</v>
       </c>
       <c r="Q5" t="n">
-        <v>2179</v>
+        <v>84</v>
       </c>
       <c r="R5" t="n">
-        <v>3774</v>
+        <v>259</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>149872454</t>
+          <t>1188195560</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/149872454</t>
+          <t>https://m.place.naver.com/place/1188195560</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스튜디오 플럼 네일 서면전포점</t>
+          <t>봄날네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gmlwjd144@naver.com</t>
+          <t>bomnal6878@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1340-2694</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 전포대로209번길 45 세진빌딩 3층</t>
+          <t>부산광역시 부산진구 가야대로482번길 90 1층 (가평초등학교 정문앞)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gmlwjd144</t>
+          <t>https://www.instagram.com/bomnalhana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>394</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1978</v>
+        <v>5</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1955645289</t>
+          <t>1853483648</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955645289</t>
+          <t>https://m.place.naver.com/place/1853483648</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1030,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>온리케어</t>
+          <t>미소샵네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>onrecare@naver.com</t>
+          <t>ehdkdlahd@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1422-8119</t>
+          <t>0507-1338-7038</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 중앙대로756번길 13 3층</t>
+          <t>부산광역시 중구 중앙대로 45 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtube.com/@BB-log</t>
+          <t>https://blog.naver.com/ehdkdlahd</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1067,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
-        <v>131</v>
+        <v>497</v>
       </c>
       <c r="R7" t="n">
-        <v>305</v>
+        <v>610</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1488037802</t>
+          <t>1824109129</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488037802</t>
+          <t>https://m.place.naver.com/place/1824109129</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>레푸스 서면점</t>
+          <t>미쯔네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mimongmnn@naver.com</t>
+          <t>mizz_nail@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1415-2301</t>
+          <t>0507-1388-3448</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 부전로 75-5 2층</t>
+          <t>부산광역시 중구 광복로 47-1 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://litt.ly/refuss_nail4season_busan</t>
+          <t>https://blog.naver.com/mizz_nail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>968</v>
+        <v>60</v>
       </c>
       <c r="Q8" t="n">
-        <v>419</v>
+        <v>24</v>
       </c>
       <c r="R8" t="n">
-        <v>1387</v>
+        <v>84</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36208933</t>
+          <t>1942024821</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36208933</t>
+          <t>https://m.place.naver.com/place/1942024821</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엔피케어 부산서면점</t>
+          <t>베스트앤뷰티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>np_care@naver.com</t>
+          <t>ringo0807@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1429-7661</t>
+          <t>0507-1442-9203</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 가야대로 781-1 4층</t>
+          <t>부산광역시 부산진구 가야대로 450 201호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/NPCARE_</t>
+          <t>https://www.instagram.com/best__beauty1/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,7 +1266,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>624</v>
+        <v>897</v>
       </c>
       <c r="Q9" t="n">
-        <v>157</v>
+        <v>230</v>
       </c>
       <c r="R9" t="n">
-        <v>781</v>
+        <v>1127</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1128716087</t>
+          <t>1803632839</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1128716087</t>
+          <t>https://m.place.naver.com/place/1803632839</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>닥터페디 서면점</t>
+          <t>미요네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>drpedi_ounail@naver.com</t>
+          <t>dago1988@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>051-808-5484</t>
+          <t>0507-1386-9536</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 38 1층</t>
+          <t>부산광역시 서구 구덕로315번길 65 . 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drpedi_ounail</t>
+          <t>https://www.instagram.com/miyonail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,17 +1365,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="Q10" t="n">
-        <v>556</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>704</v>
+        <v>264</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1551730003</t>
+          <t>1480887460</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1551730003</t>
+          <t>https://m.place.naver.com/place/1480887460</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1406,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>매료네일in뷰티</t>
+          <t>오늘,네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>girei9580@naver.com</t>
+          <t>bb_syun126@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1337-1011</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 가야대로784번길 15 3층</t>
+          <t>부산광역시 영도구 대교로 15 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maeryonail.official</t>
+          <t>http://www.instagram.com/2day__nail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>813</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1033</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1846</v>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1474,7523 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1407803013</t>
+          <t>1924350921</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407803013</t>
+          <t>https://m.place.naver.com/place/1924350921</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>정감네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jeongamnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1400-9669</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 전포대로216번길 20 3층 정감네일</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jeongamnail</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>52</v>
+      </c>
+      <c r="R12" t="n">
+        <v>124</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1378922818</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1378922818</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>네일 더 하이라이트</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ggom7811@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1465-7817</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서전로37번길 19-1 2층 네일 더 하이라이트</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ggom7811</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>44</v>
+      </c>
+      <c r="R13" t="n">
+        <v>52</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1076353493</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1076353493</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>바르샤네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>icu3675@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1409-8679</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 신암로 66 범천LH아파트 상가동 1층 111호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>355920718</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/355920718</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>네일블리</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>mmsshh0070@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1351-6041</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 광복로55번길 9 2층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>13</v>
+      </c>
+      <c r="R15" t="n">
+        <v>14</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1179997656</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1179997656</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>늘네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>gamejaki@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1484-5043</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 가야대로482번길 74 1층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ERMXb</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1150924080</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1150924080</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LK</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ans753951@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1414-7765</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 범곡서로 6 404호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1409269830</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1409269830</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>뷰티데이</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1208_sj@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1369-7116</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 구덕로 12-1 도시철도 남포역 지하상가 21호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>128</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2080886215</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2080886215</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>맑은내일</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ppspr@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 대영로 54</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>208</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>208</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1064001334</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1064001334</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>네일엠</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>kkimyuu@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1332-2366</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 대청로 125 2층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.b.m</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>487</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>491</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1433019367</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1433019367</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>윤네일</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>yungreem04@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>부산광역시 영도구 남항시장길 362</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>8</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1213572062</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213572062</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The네일샵</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hwang7486@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>051-442-4179</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 초량중로 94</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hwang7486</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>156</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>33839645</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33839645</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>네일맨숀</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jw21st@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서전로9번길 27 4층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_manshawn</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>25</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1848829737</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1848829737</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>포유 부산역지하상가점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>mh3926@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>051-466-4182</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 중앙대로 200 부산역지하상가 가8</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>31315306</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31315306</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>디아망네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>wonderfuuul@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>051-244-3998</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 구덕로 302 1층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>http://instagram.com/diamant_nail_y</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>17</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>36504745</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36504745</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>네일도,예뻐</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>nail4season@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1359-0344</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 가야대로572번길 8 1층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_wBfaK</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>188</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1888768861</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1888768861</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>두손네일 서면점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>doosonnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1382-7620</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 부전로 94 영동프라자 1층 두손네일</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dooson_nail</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>567</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1581</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2148</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1328704497</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1328704497</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>디테네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1420-3695</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>부산광역시 사하구 낙동대로 196 1층 디테네일</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ditenail_</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>107</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1399141206</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1399141206</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>남다른네일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jipguk@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1337-1029</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 초량상로 82-1 부산프라임빌 1층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jipguk</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>236</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1884465745</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1884465745</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>썸머네즈</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>summer_nezu@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1411-1294</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서전로37번길 26 A사동 2층 204호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/summer._.nezu</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>761</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>331</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1092</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1184898916</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1184898916</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>네일졍</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>nail_jyeong@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 전포대로186번길 36 4층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail_jyeong</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>29</v>
+      </c>
+      <c r="R31" t="n">
+        <v>58</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1654748003</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1654748003</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>네일온나</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dong_fcpae@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1383-4154</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 구덕로 51 3층 네일온나</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_on_na/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>377</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>13</v>
+      </c>
+      <c r="R32" t="n">
+        <v>390</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1810946003</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1810946003</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>젤리네일</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ooeqq80@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 중구로53번길 3 2층(부평동1가)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ooeqq80</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1845301385</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845301385</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>히쿠네일&amp;속눈썹 서면전포점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>hikoo_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1359-0641</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서전로46번길 80 1층 히쿠네일&amp;속눈썹 서면전포점</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hikoo_nail</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>352</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>249</v>
+      </c>
+      <c r="R34" t="n">
+        <v>601</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1129176625</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1129176625</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>네일드씨니</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>cine_scent@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 광복로 96 3층, 네일드씨니</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/naildecini</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>13</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1747678006</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1747678006</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>리체네일&amp;속눈썹 개금점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>honey9561@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 가야대로 450 상가동 B218호 리체네일</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/riche__nail</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>2463</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>384</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2847</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1708618949</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1708618949</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>네일 무이</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1347-2687</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 동성로49번길 26 2층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_mui_</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>39</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1481362742</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1481362742</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>네일비</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>panic9861@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 대영로45번길 20 1층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_b88</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>24</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1503413443</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1503413443</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>네일 십이월</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>cooler0314@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1312-2546</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서전로38번길 41 2층 201호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_12months</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>65</v>
+      </c>
+      <c r="R39" t="n">
+        <v>197</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1566394845</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1566394845</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>쏘블링네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1367-1696</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 흑교로 83-1 3층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sso_blingnail</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>650</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>20</v>
+      </c>
+      <c r="R40" t="n">
+        <v>670</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1946317931</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1946317931</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>미야비네일</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>33ehddks@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>051-247-5959</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 중구로24번길 21-1</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>8</v>
+      </c>
+      <c r="R41" t="n">
+        <v>10</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>37813819</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37813819</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>제이네일</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>morningapple6@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 대영로30번길 16-1 1층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1526699869</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1526699869</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>엘리샤네일</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>skyww5425@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>부산광역시 사하구 낙동대로 191-1 2층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>http://elysianail.7x7.kr</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>8</v>
+      </c>
+      <c r="R43" t="n">
+        <v>23</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>31301420</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31301420</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>네일,또봐</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>lyj3937@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 가야공원로52번길 12 1층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailddoba__</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>24</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2079869421</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2079869421</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>현이네일</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>c_ji_h@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1381-9527</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 신암로25번길 5 1층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/h2__nail/</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>77</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1601109899</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1601109899</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>모던네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>modern_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1303-0919</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 범일로 134 5층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/modern_nail19</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>63</v>
+      </c>
+      <c r="R46" t="n">
+        <v>63</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1630668997</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1630668997</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>피슈네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>staywithher@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1326-0117</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 고관로 71-1 1층 피슈네일</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1921095810</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1921095810</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>키스카네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>uinawe@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1327-2123</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 범일로 134 중앙귀금속상가 303호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/kisca_nail</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1047985157</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1047985157</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>엠씨네일 서면2호점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>soulkangs@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1357-2081</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 가야대로784번길 21</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mc_nail2017/</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1119</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1244</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2363</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1167495144</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1167495144</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>hackerstalk11@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1404-8964</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 대영로30번길 20 1층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>http://카카오채널:서대신썸네일</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>21</v>
+      </c>
+      <c r="R50" t="n">
+        <v>35</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1685272433</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1685272433</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>모어이브네일 서면점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>moreevenail@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1376-4422</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서전로10번길 16 3층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/moreevenail</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>783</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>40</v>
+      </c>
+      <c r="R51" t="n">
+        <v>823</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1135587389</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1135587389</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>달리뷰띠끄</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sonmh1122@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 구덕로 54-1 2층 203호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xnYigT</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>4157</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>395</v>
+      </c>
+      <c r="R52" t="n">
+        <v>4552</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1025786243</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1025786243</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>빼어날수nail</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>soonail15@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 중앙대로231번길 52 1층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>http://instagram.com/k.suin0923</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1726623623</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1726623623</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>뷰티바이정 부산범일점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>beauty_by_j_@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1362-0643</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 범일로 82 2층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beauty_by_.j</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>10</v>
+      </c>
+      <c r="R54" t="n">
+        <v>74</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1332294520</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332294520</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>뉴로우네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0640am@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1433-2164</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서전로46번길 85 4층 , 뉴로우네일</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_Zfxemn</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>585</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>7</v>
+      </c>
+      <c r="R55" t="n">
+        <v>592</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2092120640</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2092120640</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MALEN NAIL STUDOI 마렌네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>coolred955@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1306-1863</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 광복중앙로33번길 15-1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/malen_n_studio</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1331464563</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1331464563</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>더블랙뷰티 부민점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>theblackbeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1376-5423</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 구덕로 214 3층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_FyFcn</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>125</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2002868588</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002868588</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>네일바이아티제</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>pzv321@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1413-0572</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서전로47번길 25 2층 203호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_by_artisee/profilecard/?igsh=dm5ka3M2ejJtZm9i</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>85</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1962707196</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1962707196</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>뷰티나리</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>beautyna_r@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1415-0660</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 범일로 111 4층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beautyna_r</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>367</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>25</v>
+      </c>
+      <c r="R59" t="n">
+        <v>392</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1855981247</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1855981247</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>네일하자오늘</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>algus744@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1307-7173</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 구덕로339번길 39 1층 네일하자오늘</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>http://instagram.com/sj_7173</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>80</v>
+      </c>
+      <c r="R60" t="n">
+        <v>83</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1139948447</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1139948447</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>달달네일</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>wjddsmtjs@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1308-9584</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 광복중앙로 12 나투라에스테 3F 달달네일</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/daldalnail/</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>5</v>
+      </c>
+      <c r="R61" t="n">
+        <v>5</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1211702282</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1211702282</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>안녕네일보자</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>whiteangelsk@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1308-0559</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 충무대로 237-1</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/hello_nailboja</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>4</v>
+      </c>
+      <c r="R62" t="n">
+        <v>4</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1301393954</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1301393954</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>달,네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 부산진성공원로 1 달,네일 1층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dal__nail</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>3</v>
+      </c>
+      <c r="R63" t="n">
+        <v>34</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1972872334</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1972872334</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>네일그림</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>daonnail0305@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 엄광로 56 1층 네일그림</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2</v>
+      </c>
+      <c r="R64" t="n">
+        <v>16</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1272265478</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1272265478</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>JALHAE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>neona_jalhae@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1418-0915</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 대청로35번길 3 1층 민들레미용실안</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s5cpdMOh</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>89</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2014599026</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2014599026</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>예쁜손톱방</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>hina_lanayahgas@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1337-2616</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>부산광역시 사상구 학감대로 109-14 상가동 1층 101호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/yebbeun_nail_bang</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>20</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1237764066</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1237764066</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>바루나뷰티</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>tjej486@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>051-243-4144</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 흑교로31번길 3</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/varunabeauty?igsh=MWJyczF5dW05amExOA==</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3</v>
+      </c>
+      <c r="R67" t="n">
+        <v>24</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1263734981</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1263734981</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>엘카나네일</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ghktkf3409@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1361-5068</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 중앙대로 722-9 4층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_elkana?igsh=cWY5dm1zdnVnc2k1</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2</v>
+      </c>
+      <c r="R68" t="n">
+        <v>166</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2035763107</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2035763107</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>네일신</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>kooys1964@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>051-466-4022</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 고관로 79-2</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3</v>
+      </c>
+      <c r="R69" t="n">
+        <v>12</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1465714076</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1465714076</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>네일피오르</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sssong__2@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1334-4587</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 전포대로186번길 6-1 1층 네일피오르</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sssong__2</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>13</v>
+      </c>
+      <c r="R70" t="n">
+        <v>456</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1363067996</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1363067996</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>디즈네일</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>aijungmal90@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1342-2840</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>부산광역시 사하구 낙동대로 280 304동 B106호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sEVHZD4b</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>64</v>
+      </c>
+      <c r="R71" t="n">
+        <v>360</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1834431145</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1834431145</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>제이린네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>immire@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1430-9486</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 범일로153번길 3 2층 제이린네일</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/j.lin_nail</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1492</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>11</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1503</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1708955952</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1708955952</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>유경 더뷰티</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>doak0819@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1357-4575</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>부산광역시 사하구 사리로46번길 12 유경 더뷰티</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/doak0819</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>50</v>
+      </c>
+      <c r="R73" t="n">
+        <v>93</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1436202813</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1436202813</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>네일윤</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>lovelyanne201@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 구덕로 12-1 12, 남포역지하상가 25호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" t="n">
+        <v>98</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1341425438</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1341425438</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>살롱드문</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>dhfpdk4000@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1344-7987</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>부산광역시 남구 황령대로74번길 48 2층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>http://instagram.com/salonde_moon</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>3</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1342265826</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1342265826</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>오늘네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>barbie0903@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1322-5541</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 범일로 108 지하상가 16호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/onl.nail</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1399529949</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1399529949</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>드블랑 뷰티</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>haeri_c@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서전로68번길 59-5 3층</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/deblanc__beauty</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>6</v>
+      </c>
+      <c r="R77" t="n">
+        <v>447</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1200798214</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1200798214</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>유주네일</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>cutty_julia@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1448-1805</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 대청로 98-1 1층</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>http://instagram.com/yujunail</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>12</v>
+      </c>
+      <c r="R78" t="n">
+        <v>15</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1262268563</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1262268563</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>와와네일</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ynana1@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1389-8270</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 범일로154번길 33 풍림아이원 상가 1층 1014호</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wawanail_</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>712</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>23</v>
+      </c>
+      <c r="R79" t="n">
+        <v>735</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1329962455</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1329962455</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>아우어즈네일샵</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1382-6863</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서전로38번길 9-7 3층</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_IxfVxoG</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>4</v>
+      </c>
+      <c r="R80" t="n">
+        <v>125</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1738313201</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1738313201</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>COCO</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>exaggerate1864@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>051-633-8027</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 범일로 120 2층</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>52</v>
+      </c>
+      <c r="R81" t="n">
+        <v>119</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>21492112</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21492112</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>영네일</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>cy2403@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 신천대로65번길 9 105호</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_qMbCG</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>11</v>
+      </c>
+      <c r="R82" t="n">
+        <v>72</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1330934813</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1330934813</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>루미엘네일살롱</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ji0eun2@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 자갈치로59번길 5-21 1층 루미엘네일살롱</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lumiere_nailbin</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>5</v>
+      </c>
+      <c r="R83" t="n">
+        <v>34</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1816317306</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1816317306</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>눈네일</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>yunimil@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1350-2086</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 해관로 22-1 3층</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/noonnail</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>8</v>
+      </c>
+      <c r="R84" t="n">
+        <v>17</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1509715865</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1509715865</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>비비네일앤속눈썹</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>mcdud@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1420-8093</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 서면로 53 2층</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/bibinail_love</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>890</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2616</v>
+      </c>
+      <c r="R85" t="n">
+        <v>3506</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>34658448</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34658448</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>섬섬옥수</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>hohaho1541@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 중앙대로 210 부산역2F</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>9</v>
+      </c>
+      <c r="R86" t="n">
+        <v>9</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1290753909</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1290753909</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>다이네일</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 동천로95번길 6 3층 에스티로 헤어</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dyenail_</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>32</v>
+      </c>
+      <c r="R87" t="n">
+        <v>167</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1393677308</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1393677308</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>네일리안</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>dhfpswl3609@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>051-242-2822</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 구덕로 117 1층 네일리안</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>10</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1778026654</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1778026654</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>그래이네일</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>pej8976@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 흑교로46번길 3-1 1층 그래이네일샵</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>http://instagram.com/grae_enail</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>2</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1226844863</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1226844863</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>남포동네일옐로</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>suhyun5618@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1378-0493</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 남포동1가 11 41호</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>10</v>
+      </c>
+      <c r="R90" t="n">
+        <v>322</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1003177563</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1003177563</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>코코네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>cion6490@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1319-9364</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>부산광역시 남구 전포대로20번길 26 1층 첫번째상가 코코레브로 오세요</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coco_reve_nail_official?igsh=MW45MXFrMG1kaWl2Yw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>44</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>2007701185</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2007701185</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>뮤이즈네일스튜디오 전포점</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>jeongvely23@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1378-3752</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>부산광역시 부산진구 전포대로255번길 37 다동 111호</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muiz_nail?igsh=ZnR5YWptZ3FoZXE2&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>578</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>11</v>
+      </c>
+      <c r="R92" t="n">
+        <v>589</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1128193244</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1128193244</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
